--- a/exports/MANAPPURAM_full_report.xlsx
+++ b/exports/MANAPPURAM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.91</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>162.35</v>
+        <v>157.75</v>
       </c>
       <c r="I2" t="n">
         <v>160.115040381665</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.13</v>
+        <v>-6.85</v>
       </c>
       <c r="L2" t="n">
-        <v>5.99</v>
+        <v>7.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.93</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.86</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.07</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>113.7</v>
+        <v>120.85</v>
       </c>
       <c r="I3" t="n">
         <v>119.1478107040769</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K3" t="n">
-        <v>27.92</v>
+        <v>23.39</v>
       </c>
       <c r="L3" t="n">
         <v>2.63</v>
@@ -612,7 +647,7 @@
         <v>3.98</v>
       </c>
       <c r="N3" t="n">
-        <v>6.03</v>
+        <v>6.33</v>
       </c>
       <c r="O3" t="n">
         <v>-4.1</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.85</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>121.25</v>
+        <v>116.45</v>
       </c>
       <c r="I4" t="n">
         <v>116.9083538453221</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>0.33</v>
+        <v>-3.64</v>
       </c>
       <c r="L4" t="n">
         <v>6.04</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.24</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44743.55208333334</v>
+        <v>44746.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>88.25</v>
+        <v>90.5</v>
       </c>
       <c r="I5" t="n">
         <v>89.28099618514932</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>73</v>
+        <v>75.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>24.22</v>
+        <v>22.28</v>
       </c>
       <c r="L5" t="n">
         <v>5.07</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>7.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>103.45</v>
+        <v>100.55</v>
       </c>
       <c r="I6" t="n">
         <v>101.9409108154611</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>14.31</v>
+        <v>11.1</v>
       </c>
       <c r="L6" t="n">
         <v>3.65</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>3.13</v>
+        <v>3.87</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>98.40000000000001</v>
+        <v>101.05</v>
       </c>
       <c r="I7" t="n">
         <v>98.78618054649162</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K7" t="n">
-        <v>2.14</v>
+        <v>-0.5</v>
       </c>
       <c r="L7" t="n">
         <v>7.81</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.99</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>119</v>
+        <v>116.55</v>
       </c>
       <c r="I8" t="n">
         <v>116.8967327512169</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K8" t="n">
-        <v>17.76</v>
+        <v>15.34</v>
       </c>
       <c r="L8" t="n">
         <v>2.13</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.37</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44925.55208333334</v>
+        <v>44928.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>116.3</v>
+        <v>119.45</v>
       </c>
       <c r="I9" t="n">
         <v>117.515857768125</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>0.21</v>
+        <v>-2.49</v>
       </c>
       <c r="L9" t="n">
         <v>5.28</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>7.83</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44943.55208333334</v>
+        <v>44944.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>117.75</v>
+        <v>115.6</v>
       </c>
       <c r="I10" t="n">
         <v>117.1478319220118</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.42</v>
+        <v>-3.22</v>
       </c>
       <c r="L10" t="n">
-        <v>2.76</v>
+        <v>3.93</v>
       </c>
       <c r="M10" t="n">
         <v>0.13</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.49</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>105.85</v>
+        <v>109.9</v>
       </c>
       <c r="I11" t="n">
         <v>107.6026423439567</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K11" t="n">
-        <v>8.43</v>
+        <v>4.93</v>
       </c>
       <c r="L11" t="n">
         <v>4.11</v>
@@ -1068,7 +1199,7 @@
         <v>3.43</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
         <v>-0.38</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.59</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>110.95</v>
+        <v>109.6</v>
       </c>
       <c r="I12" t="n">
         <v>110.3919550870935</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.96</v>
+        <v>-0.27</v>
       </c>
       <c r="L12" t="n">
         <v>2.59</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.66</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45005.55208333334</v>
+        <v>45006.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>113.2</v>
+        <v>117.15</v>
       </c>
       <c r="I13" t="n">
         <v>116.7382892215599</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.28</v>
+        <v>-6.89</v>
       </c>
       <c r="L13" t="n">
         <v>9.029999999999999</v>
@@ -1182,7 +1337,7 @@
         <v>6.32</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="O13" t="n">
         <v>-0.86</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.02</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45009.55208333334</v>
+        <v>45012.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>117.15</v>
+        <v>113.55</v>
       </c>
       <c r="I14" t="n">
         <v>113.9515809960581</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-3.07</v>
       </c>
       <c r="L14" t="n">
         <v>3.37</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>9.34</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45014.38541666666</v>
+        <v>45014.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I15" t="n">
         <v>122.5701977084863</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.68</v>
+        <v>-8.32</v>
       </c>
       <c r="L15" t="n">
-        <v>5.68</v>
+        <v>8.81</v>
       </c>
       <c r="M15" t="n">
         <v>0.73</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>7.98</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45048.55208333334</v>
+        <v>45049.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>129.9</v>
+        <v>112.2</v>
       </c>
       <c r="I16" t="n">
         <v>124.6512535590817</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K16" t="n">
-        <v>5.61</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>9.23</v>
       </c>
       <c r="M16" t="n">
         <v>0.67</v>
       </c>
       <c r="N16" t="n">
-        <v>1.86</v>
+        <v>12.36</v>
       </c>
       <c r="O16" t="n">
         <v>3.36</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>16.68</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45085.55208333334</v>
+        <v>45086.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>112.5</v>
+        <v>116.8</v>
       </c>
       <c r="I17" t="n">
         <v>115.339831353793</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.27</v>
+        <v>-4.1</v>
       </c>
       <c r="L17" t="n">
         <v>15.55</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.64</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45120.38541666666</v>
+        <v>45120.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>128.15</v>
+        <v>123.95</v>
       </c>
       <c r="I18" t="n">
         <v>124.7928955600691</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K18" t="n">
-        <v>9.720000000000001</v>
+        <v>6.12</v>
       </c>
       <c r="L18" t="n">
         <v>2.91</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.44</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45132.55208333334</v>
+        <v>45133.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>130</v>
+        <v>134.45</v>
       </c>
       <c r="I19" t="n">
         <v>132.8306150906613</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.88</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>7.14</v>
+        <v>9.68</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="O19" t="n">
         <v>-3.88</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.88</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45162.55208333334</v>
+        <v>45163.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>142.15</v>
+        <v>140.3</v>
       </c>
       <c r="I20" t="n">
         <v>141.3386652217727</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K20" t="n">
-        <v>5.73</v>
+        <v>4.35</v>
       </c>
       <c r="L20" t="n">
         <v>3.38</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>7.17</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45168.55208333334</v>
+        <v>45169.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>148.7</v>
+        <v>152.5</v>
       </c>
       <c r="I21" t="n">
         <v>150.195466380641</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.99</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>6.91</v>
+        <v>10.98</v>
       </c>
       <c r="M21" t="n">
         <v>1.74</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>3.77</v>
       </c>
       <c r="O21" t="n">
         <v>-1.37</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>6.96</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>148.75</v>
+        <v>140.45</v>
       </c>
       <c r="I22" t="n">
         <v>143.6739499645845</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.46</v>
+        <v>-7.9</v>
       </c>
       <c r="L22" t="n">
-        <v>5.44</v>
+        <v>9.18</v>
       </c>
       <c r="M22" t="n">
         <v>0.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.79</v>
+        <v>7.63</v>
       </c>
       <c r="O22" t="n">
         <v>3.77</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>11.36</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45196.55208333334</v>
+        <v>45197.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>147.1</v>
+        <v>149.5</v>
       </c>
       <c r="I23" t="n">
         <v>147.2439350943025</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.73</v>
+        <v>-6.44</v>
       </c>
       <c r="L23" t="n">
-        <v>7.23</v>
+        <v>7.44</v>
       </c>
       <c r="M23" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="N23" t="n">
         <v>4.33</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>6.73</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45204.38541666666</v>
+        <v>45204.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>141.65</v>
+        <v>140.45</v>
       </c>
       <c r="I24" t="n">
         <v>140.9096976982674</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.25</v>
+        <v>-6.05</v>
       </c>
       <c r="L24" t="n">
-        <v>5.92</v>
+        <v>6.69</v>
       </c>
       <c r="M24" t="n">
         <v>0.8</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.42</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45233.55208333334</v>
+        <v>45236.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>139.8</v>
+        <v>142.85</v>
       </c>
       <c r="I25" t="n">
         <v>140.1475834731376</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>29</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>-1.71</v>
       </c>
       <c r="L25" t="n">
         <v>5.48</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45301.38541666666</v>
+        <v>45301.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>168.4</v>
+        <v>167.9</v>
       </c>
       <c r="I26" t="n">
         <v>168.308409046743</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>65</v>
+        <v>65.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>17.89</v>
+        <v>17.54</v>
       </c>
       <c r="L26" t="n">
         <v>5.92</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>8.07</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45320.55208333334</v>
+        <v>45321.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>180</v>
+        <v>186.75</v>
       </c>
       <c r="I27" t="n">
         <v>181.4427948049244</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.21</v>
+        <v>-11.23</v>
       </c>
       <c r="L27" t="n">
-        <v>9.109999999999999</v>
+        <v>12.09</v>
       </c>
       <c r="M27" t="n">
         <v>1.16</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>179.3</v>
+        <v>172.8</v>
       </c>
       <c r="I28" t="n">
         <v>174.3603868817222</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.99</v>
+        <v>-7.47</v>
       </c>
       <c r="L28" t="n">
         <v>8.94</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,25 +2420,25 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45355.55208333334</v>
+        <v>45356.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>183.7</v>
+        <v>189.75</v>
       </c>
       <c r="I29" t="n">
         <v>184.4362426089719</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.31</v>
+        <v>-9.81</v>
       </c>
       <c r="L29" t="n">
-        <v>7.03</v>
+        <v>15.16</v>
       </c>
       <c r="M29" t="n">
-        <v>1.22</v>
+        <v>2.07</v>
       </c>
       <c r="N29" t="n">
         <v>2.64</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>6.06</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45356.55208333334</v>
+        <v>45357.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>186</v>
+        <v>171.95</v>
       </c>
       <c r="I30" t="n">
         <v>178.2556411018282</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.98</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>2.16</v>
+        <v>11.09</v>
       </c>
       <c r="M30" t="n">
         <v>-0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="O30" t="n">
         <v>1.25</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>14.49</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>174.4</v>
+        <v>179.9</v>
       </c>
       <c r="I31" t="n">
         <v>179.0759589253577</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.42</v>
+        <v>-4.62</v>
       </c>
       <c r="L31" t="n">
         <v>8.869999999999999</v>
@@ -2208,7 +2579,7 @@
         <v>1.38</v>
       </c>
       <c r="N31" t="n">
-        <v>3.72</v>
+        <v>4.47</v>
       </c>
       <c r="O31" t="n">
         <v>-6.72</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.86</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>192.5</v>
+        <v>185.2</v>
       </c>
       <c r="I32" t="n">
         <v>189.1305820004211</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K32" t="n">
-        <v>7</v>
+        <v>2.95</v>
       </c>
       <c r="L32" t="n">
         <v>2.72</v>
@@ -2265,7 +2648,7 @@
         <v>2.91</v>
       </c>
       <c r="N32" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
         <v>4.47</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10.05</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45428.38541666666</v>
+        <v>45428.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>183.6</v>
+        <v>185.5</v>
       </c>
       <c r="I33" t="n">
         <v>184.7180519741406</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>0.86</v>
+        <v>-0.16</v>
       </c>
       <c r="L33" t="n">
         <v>4.64</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>172.1</v>
+        <v>168.6</v>
       </c>
       <c r="I34" t="n">
         <v>171.8714819181231</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.22</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>8.109999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="M34" t="n">
         <v>0.52</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.97</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45450.38541666666</v>
+        <v>45450.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>177.35</v>
+        <v>178.5</v>
       </c>
       <c r="I35" t="n">
         <v>177.7648866331501</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.19</v>
+        <v>-5.87</v>
       </c>
       <c r="L35" t="n">
         <v>6.64</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.31</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>215.45</v>
+        <v>207.74</v>
       </c>
       <c r="I36" t="n">
         <v>214.4959528536436</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>45</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>20.7</v>
+        <v>16.38</v>
       </c>
       <c r="L36" t="n">
         <v>0.87</v>
@@ -2493,7 +2924,7 @@
         <v>0.29</v>
       </c>
       <c r="N36" t="n">
-        <v>4.95</v>
+        <v>5.78</v>
       </c>
       <c r="O36" t="n">
         <v>0.79</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>9.56</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45525.55208333334</v>
+        <v>45526.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>212.52</v>
+        <v>216.02</v>
       </c>
       <c r="I37" t="n">
         <v>213.5682805873752</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.3</v>
+        <v>-3.99</v>
       </c>
       <c r="L37" t="n">
-        <v>4.92</v>
+        <v>5.6</v>
       </c>
       <c r="M37" t="n">
         <v>2.36</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>6.49</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>205.51</v>
+        <v>203.53</v>
       </c>
       <c r="I38" t="n">
         <v>205.0706586473872</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.87</v>
+        <v>-5.78</v>
       </c>
       <c r="L38" t="n">
-        <v>5.48</v>
+        <v>6.14</v>
       </c>
       <c r="M38" t="n">
         <v>0.59</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>6.08</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45547.55208333334</v>
+        <v>45548.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>205.66</v>
+        <v>212.98</v>
       </c>
       <c r="I39" t="n">
         <v>211.9306086254362</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.05</v>
+        <v>-4.64</v>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>6.37</v>
       </c>
       <c r="M39" t="n">
-        <v>0.52</v>
+        <v>2.4</v>
       </c>
       <c r="N39" t="n">
-        <v>1.81</v>
+        <v>2.86</v>
       </c>
       <c r="O39" t="n">
         <v>-0.27</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>5.91</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45560.55208333334</v>
+        <v>45561.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>202.41</v>
+        <v>200.31</v>
       </c>
       <c r="I40" t="n">
         <v>201.9178349464896</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.96</v>
+        <v>-5.95</v>
       </c>
       <c r="L40" t="n">
-        <v>6.56</v>
+        <v>8.91</v>
       </c>
       <c r="M40" t="n">
         <v>3.54</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.34</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45594.55208333334</v>
+        <v>45595.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>155.6</v>
+        <v>159.91</v>
       </c>
       <c r="I41" t="n">
         <v>157.7688794675344</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K41" t="n">
-        <v>22.32</v>
+        <v>20.17</v>
       </c>
       <c r="L41" t="n">
         <v>2.97</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.87</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>182</v>
+        <v>178.28</v>
       </c>
       <c r="I42" t="n">
         <v>178.8348468277097</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K42" t="n">
-        <v>13.81</v>
+        <v>11.49</v>
       </c>
       <c r="L42" t="n">
         <v>7.65</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45674.38541666666</v>
+        <v>45674.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>187.85</v>
+        <v>195.6</v>
       </c>
       <c r="I43" t="n">
         <v>190.1173495180804</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.37</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>7.42</v>
+        <v>10.39</v>
       </c>
       <c r="M43" t="n">
         <v>4.65</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>10.62</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45701.55208333334</v>
+        <v>45702.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>194</v>
+        <v>173.81</v>
       </c>
       <c r="I44" t="n">
         <v>191.2445950044818</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.82</v>
+        <v>-11.14</v>
       </c>
       <c r="L44" t="n">
-        <v>6.65</v>
+        <v>13.69</v>
       </c>
       <c r="M44" t="n">
-        <v>0.47</v>
+        <v>3.09</v>
       </c>
       <c r="N44" t="n">
         <v>6.23</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>17.43</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45708.38541666666</v>
+        <v>45708.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>197.74</v>
+        <v>207</v>
       </c>
       <c r="I45" t="n">
         <v>202.958798896799</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-13.77</v>
+        <v>-19.1</v>
       </c>
       <c r="L45" t="n">
-        <v>18.91</v>
+        <v>19.1</v>
       </c>
       <c r="M45" t="n">
         <v>1.51</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>14.46</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>265.6</v>
+        <v>262.9</v>
       </c>
       <c r="I46" t="n">
         <v>263.7048712794253</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>155</v>
+        <v>157.8333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>28.31</v>
+        <v>27</v>
       </c>
       <c r="L46" t="n">
         <v>6.03</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>207</v>
+        <v>208</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.98</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45873.38541666666</v>
+        <v>45873.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>260.35</v>
+        <v>263.45</v>
       </c>
       <c r="I47" t="n">
         <v>262.0210761939889</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>0.97</v>
+        <v>-0.21</v>
       </c>
       <c r="L47" t="n">
         <v>1.41</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.59</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45924.55208333334</v>
+        <v>45925.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>286</v>
+        <v>281.5</v>
       </c>
       <c r="I48" t="n">
         <v>283.354301631921</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>51</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K48" t="n">
-        <v>8.56</v>
+        <v>6.85</v>
       </c>
       <c r="L48" t="n">
         <v>4.82</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>5.96</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45936.55208333334</v>
+        <v>45937.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>290.5</v>
+        <v>292.55</v>
       </c>
       <c r="I49" t="n">
         <v>291.5528856294642</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.2</v>
+        <v>-3.93</v>
       </c>
       <c r="L49" t="n">
-        <v>4.26</v>
+        <v>4.76</v>
       </c>
       <c r="M49" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="N49" t="n">
         <v>1.97</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>5.35</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45951.57291666666</v>
+        <v>45953.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>285.9</v>
+        <v>280.05</v>
       </c>
       <c r="I50" t="n">
         <v>280.1926886579679</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>14.1875</v>
+        <v>16</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.27</v>
+        <v>-4.27</v>
       </c>
       <c r="L50" t="n">
-        <v>3.33</v>
+        <v>5.01</v>
       </c>
       <c r="M50" t="n">
-        <v>0.17</v>
+        <v>1.35</v>
       </c>
       <c r="N50" t="n">
         <v>2.84</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.17</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45986.55208333334</v>
+        <v>45987.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>279</v>
+        <v>285.2</v>
       </c>
       <c r="I51" t="n">
         <v>284.2766694649138</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K51" t="n">
-        <v>0.37</v>
+        <v>-1.84</v>
       </c>
       <c r="L51" t="n">
         <v>2.23</v>
@@ -3348,7 +3959,7 @@
         <v>1.52</v>
       </c>
       <c r="N51" t="n">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="O51" t="n">
         <v>-1</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.59</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45995.38541666666</v>
+        <v>45995.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>274.05</v>
+        <v>273.5</v>
       </c>
       <c r="I52" t="n">
         <v>273.808982801987</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.91</v>
+        <v>-4.1</v>
       </c>
       <c r="L52" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="M52" t="n">
         <v>0.16</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>4.83</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46002.55208333334</v>
+        <v>46003.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>283.3</v>
+        <v>287</v>
       </c>
       <c r="I53" t="n">
         <v>284.8011585706268</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.58</v>
+        <v>-4.94</v>
       </c>
       <c r="L53" t="n">
-        <v>4.3</v>
+        <v>5.08</v>
       </c>
       <c r="M53" t="n">
         <v>1.12</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.09</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46031.38541666666</v>
+        <v>46031.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>306.15</v>
+        <v>293</v>
       </c>
       <c r="I54" t="n">
         <v>299.9120875994194</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>6.67</v>
+        <v>2.09</v>
       </c>
       <c r="L54" t="n">
-        <v>2.04</v>
+        <v>2.94</v>
       </c>
       <c r="M54" t="n">
         <v>0.74</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.06</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46059.38541666666</v>
+        <v>46059.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>293.6</v>
+        <v>300.5</v>
       </c>
       <c r="I55" t="n">
         <v>295.9398146024074</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.2</v>
+        <v>-2.56</v>
       </c>
       <c r="L55" t="n">
         <v>8.48</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>10.57</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46078.55208333334</v>
+        <v>46079.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>295.8</v>
+        <v>286.4</v>
       </c>
       <c r="I56" t="n">
         <v>290.7805077292923</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.56</v>
+        <v>-4.69</v>
       </c>
       <c r="L56" t="n">
-        <v>2.66</v>
+        <v>5.34</v>
       </c>
       <c r="M56" t="n">
-        <v>0.54</v>
+        <v>2.94</v>
       </c>
       <c r="N56" t="n">
         <v>3.51</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.32</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46099.38541666666</v>
+        <v>46099.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>268.1</v>
+        <v>271.35</v>
       </c>
       <c r="I57" t="n">
         <v>270.5267509900647</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>6.39</v>
+        <v>5.25</v>
       </c>
       <c r="L57" t="n">
         <v>3.79</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>8.43</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>259.9</v>
+        <v>245.25</v>
       </c>
       <c r="I58" t="n">
         <v>248.4833286754185</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.22</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>4.74</v>
+        <v>9.66</v>
       </c>
       <c r="M58" t="n">
-        <v>1.01</v>
+        <v>2.69</v>
       </c>
       <c r="N58" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="O58" t="n">
         <v>5.48</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>11.17</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46132.55208333334</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>269</v>
+        <v>280.55</v>
       </c>
       <c r="I59" t="n">
         <v>272.2945722342097</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K59" t="n">
-        <v>-9.68</v>
+        <v>-14.39</v>
       </c>
       <c r="L59" t="n">
-        <v>12.03</v>
+        <v>14.64</v>
       </c>
       <c r="M59" t="n">
         <v>3.64</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.66</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>297.85</v>
+        <v>292.5</v>
       </c>
       <c r="I60" t="n">
         <v>297.4760094786394</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>6.17</v>
+        <v>4.26</v>
       </c>
       <c r="L60" t="n">
         <v>3.72</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>7.94</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46161.55208333334</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>315.35</v>
+        <v>320.25</v>
       </c>
       <c r="I61" t="n">
         <v>315.7233054716624</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.81</v>
+        <v>-9.49</v>
       </c>
       <c r="L61" t="n">
-        <v>8.029999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="M61" t="n">
         <v>3.09</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>8.31</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46174.55208333334</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>317</v>
+        <v>310.4</v>
       </c>
       <c r="I62" t="n">
         <v>311.423886126873</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.01</v>
+        <v>-3.08</v>
       </c>
       <c r="L62" t="n">
-        <v>2.76</v>
+        <v>4.2</v>
       </c>
       <c r="M62" t="n">
         <v>0.75</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>6.77</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>304.6</v>
+        <v>319.05</v>
       </c>
       <c r="I63" t="n">
         <v>310.641686367275</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K63" t="n">
-        <v>1.87</v>
+        <v>-2.79</v>
       </c>
       <c r="L63" t="n">
-        <v>1.93</v>
+        <v>2.9</v>
       </c>
       <c r="M63" t="n">
         <v>2.34</v>
       </c>
       <c r="N63" t="n">
-        <v>4.17</v>
+        <v>4.4</v>
       </c>
       <c r="O63" t="n">
         <v>-0.95</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>9.43</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46246.55208333334</v>
+        <v>46247.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>354.6</v>
+        <v>345.8</v>
       </c>
       <c r="I64" t="n">
         <v>353.3282749066963</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K64" t="n">
-        <v>11.14</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L64" t="n">
         <v>4.12</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>8.35</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46255.55208333334</v>
+        <v>46258.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>357.45</v>
+        <v>366.55</v>
       </c>
       <c r="I65" t="n">
         <v>357.9356706264383</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.37</v>
+        <v>-6</v>
       </c>
       <c r="L65" t="n">
-        <v>3.67</v>
+        <v>6.97</v>
       </c>
       <c r="M65" t="n">
         <v>1.7</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>6.44</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46260.55208333334</v>
+        <v>46261.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>367.25</v>
+        <v>348</v>
       </c>
       <c r="I66" t="n">
         <v>350.5343791169873</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>0.19</v>
+        <v>-5.06</v>
       </c>
       <c r="L66" t="n">
-        <v>2.25</v>
+        <v>5.47</v>
       </c>
       <c r="M66" t="n">
-        <v>0.04</v>
+        <v>0.5</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="O66" t="n">
         <v>2.22</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46290.38541666666</v>
+        <v>46290.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>329.8</v>
+        <v>333.9</v>
       </c>
       <c r="I67" t="n">
         <v>333.3782083362453</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>5.23</v>
+        <v>4.05</v>
       </c>
       <c r="L67" t="n">
         <v>6.29</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.73</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>316.35</v>
+        <v>307.85</v>
       </c>
       <c r="I68" t="n">
         <v>311.4214861228771</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K68" t="n">
-        <v>-5.26</v>
+        <v>-7.8</v>
       </c>
       <c r="L68" t="n">
-        <v>7.59</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M68" t="n">
         <v>1.77</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>8.68</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46308.38541666666</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>320.55</v>
+        <v>324.95</v>
       </c>
       <c r="I69" t="n">
         <v>324.3927475451052</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.13</v>
+        <v>-5.55</v>
       </c>
       <c r="L69" t="n">
-        <v>4.97</v>
+        <v>5.86</v>
       </c>
       <c r="M69" t="n">
         <v>0.97</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>6.31</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>318</v>
+        <v>301.25</v>
       </c>
       <c r="I70" t="n">
         <v>307.9413319607742</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>6</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.14</v>
+        <v>-7.29</v>
       </c>
       <c r="L70" t="n">
-        <v>2.69</v>
+        <v>7.85</v>
       </c>
       <c r="M70" t="n">
         <v>0.63</v>
       </c>
       <c r="N70" t="n">
-        <v>1.94</v>
+        <v>5.03</v>
       </c>
       <c r="O70" t="n">
         <v>1.42</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>10</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>157.8</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7510,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7520,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7530,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>73.90000000000001</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.73</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.35</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28.31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.34</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.92</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7610,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.91</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7630,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="25">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.73</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7670,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.96</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
